--- a/outputs/templates/成本法测算_模板.xlsx
+++ b/outputs/templates/成本法测算_模板.xlsx
@@ -849,7 +849,7 @@
         </is>
       </c>
       <c r="C14" s="16">
-        <f>SUM(C6:C12)</f>
+        <f>ROUND(SUM(C6:C12),0)</f>
         <v/>
       </c>
     </row>
@@ -1029,7 +1029,7 @@
         </is>
       </c>
       <c r="B13" s="20">
-        <f>(B5-B6)*MAX(0,MIN(1,B7/B8))</f>
+        <f>ROUND((B5-B6)*MAX(0,MIN(1,B7/B8)),0)</f>
         <v/>
       </c>
       <c r="C13" s="19" t="inlineStr">
@@ -1045,7 +1045,7 @@
         </is>
       </c>
       <c r="B14" s="20">
-        <f>B5*(1-B9)</f>
+        <f>ROUND(B5*(1-B9),0)</f>
         <v/>
       </c>
       <c r="C14" s="19" t="inlineStr">
@@ -1100,7 +1100,7 @@
         </is>
       </c>
       <c r="B19" s="25">
-        <f>IF(B4="年龄-寿命法",B13,IF(B4="成新折扣法",B14,B15+B16+B17))</f>
+        <f>ROUND(IF(B4="年龄-寿命法",B13,IF(B4="成新折扣法",B14,B15+B16+B17)),0)</f>
         <v/>
       </c>
       <c r="C19" s="26" t="inlineStr">
@@ -1208,7 +1208,7 @@
         </is>
       </c>
       <c r="B7" s="27">
-        <f>B4-B5+B6</f>
+        <f>ROUND(B4-B5+B6,0)</f>
         <v/>
       </c>
     </row>
@@ -1227,7 +1227,7 @@
         </is>
       </c>
       <c r="B10" s="27">
-        <f>B7*B9</f>
+        <f>ROUND(B7*B9,0)</f>
         <v/>
       </c>
     </row>

--- a/outputs/templates/成本法测算_模板.xlsx
+++ b/outputs/templates/成本法测算_模板.xlsx
@@ -730,12 +730,12 @@
         </is>
       </c>
       <c r="C8" s="10">
-        <f>ROUND(C7*管理费率,0)</f>
+        <f>ROUND(C7*$F$8,0)</f>
         <v/>
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>公式: 管理费率 × 建设成本. 管理费率填在C8旁</t>
+          <t>公式: 管理费率($F$8) × 建设成本</t>
         </is>
       </c>
       <c r="E8" s="11" t="inlineStr">
@@ -743,7 +743,9 @@
           <t>管理费率</t>
         </is>
       </c>
-      <c r="F8" s="12" t="n"/>
+      <c r="F8" s="12" t="n">
+        <v>0.03</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="n">
@@ -755,12 +757,12 @@
         </is>
       </c>
       <c r="C9" s="10">
-        <f>ROUND(售价*销售费率,0)</f>
+        <f>ROUND(C14*$F$9,0)</f>
         <v/>
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>公式: 销售费率 × 售价. 销售费率填在C9旁</t>
+          <t>公式: 售价参考行C14 × 销售费率($F$9)</t>
         </is>
       </c>
       <c r="E9" s="11" t="inlineStr">
@@ -768,7 +770,9 @@
           <t>销售费率</t>
         </is>
       </c>
-      <c r="F9" s="12" t="n"/>
+      <c r="F9" s="12" t="n">
+        <v>0.02</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="n">
@@ -780,12 +784,12 @@
         </is>
       </c>
       <c r="C10" s="10">
-        <f>ROUND(C6*利率*计息期+C7*利率*计息期/2,0)</f>
+        <f>ROUND((C6+C7)*$F$10,0)</f>
         <v/>
       </c>
       <c r="D10" s="9" t="inlineStr">
         <is>
-          <t>利率填在C10旁. 不含C9/C11. 4.4.6条第2款</t>
+          <t>公式: (土地成本+建设成本) × 年利率($F$10). 不含C9/C11. 4.4.6条第2款</t>
         </is>
       </c>
       <c r="E10" s="11" t="inlineStr">
@@ -793,7 +797,9 @@
           <t>利率</t>
         </is>
       </c>
-      <c r="F10" s="13" t="n"/>
+      <c r="F10" s="13" t="n">
+        <v>0.04</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="n">
@@ -805,12 +811,12 @@
         </is>
       </c>
       <c r="C11" s="10">
-        <f>ROUND(售价*税率,0)</f>
+        <f>ROUND(C14*$F$11,0)</f>
         <v/>
       </c>
       <c r="D11" s="9" t="inlineStr">
         <is>
-          <t>公式: 税率 × 售价. 税率填在C11旁</t>
+          <t>公式: 售价参考行C14 × 税率($F$11)</t>
         </is>
       </c>
       <c r="E11" s="11" t="inlineStr">
@@ -818,7 +824,9 @@
           <t>税率</t>
         </is>
       </c>
-      <c r="F11" s="12" t="n"/>
+      <c r="F11" s="12" t="n">
+        <v>0.05</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="n">
@@ -832,7 +840,7 @@
       <c r="C12" s="14" t="n"/>
       <c r="D12" s="9" t="inlineStr">
         <is>
-          <t>计算基数×利润率. 4.4.6条. 黄底=关键参数</t>
+          <t>计算基数×利润率($F$12). 4.4.6条. 黄底=关键参数</t>
         </is>
       </c>
       <c r="E12" s="11" t="inlineStr">
@@ -840,7 +848,9 @@
           <t>利润率</t>
         </is>
       </c>
-      <c r="F12" s="12" t="n"/>
+      <c r="F12" s="12" t="n">
+        <v>0.12</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="15" t="inlineStr">

--- a/outputs/templates/成本法测算_模板.xlsx
+++ b/outputs/templates/成本法测算_模板.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重置成本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="折旧测算" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本价值" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="重置成本" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="折旧测算" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="成本价值" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/outputs/templates/成本法测算_模板.xlsx
+++ b/outputs/templates/成本法测算_模板.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="重置成本" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="折旧测算" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="成本价值" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="重置成本" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="折旧测算" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="成本价值" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
